--- a/Project_ETF/ETF_Investment_Portfolio/00403A/ETF_Investment_Portfolio_20260716.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00403A/ETF_Investment_Portfolio_20260716.xlsx
@@ -616,7 +616,7 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>18.98%</t>
+          <t>19.52%</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>7.57%</t>
+          <t>7.41%</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>4.54%</t>
+          <t>4.74%</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>4.39%</t>
+          <t>4.25%</t>
         </is>
       </c>
     </row>
@@ -704,7 +704,7 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>4.02%</t>
+          <t>3.85%</t>
         </is>
       </c>
     </row>
@@ -726,7 +726,7 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>3.85%</t>
+          <t>3.84%</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>3.78%</t>
+          <t>3.74%</t>
         </is>
       </c>
     </row>
@@ -770,7 +770,7 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>3.64%</t>
+          <t>3.66%</t>
         </is>
       </c>
     </row>
@@ -792,117 +792,117 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>3.52%</t>
+          <t>3.51%</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>智邦</t>
+          <t>台達電</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>2,100,000</t>
+          <t>2,600,000</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>2.99%</t>
+          <t>3.06%</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>智邦</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>2,530,000</t>
+          <t>2,100,000</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.91%</t>
+          <t>3.01%</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>4958</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>臻鼎-KY</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>6,940,000</t>
+          <t>6,150,000</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.61%</t>
+          <t>2.59%</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>5,900,000</t>
+          <t>790,000</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2.45%</t>
+          <t>2.50%</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>4958</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>臻鼎-KY</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>790,000</t>
+          <t>6,940,000</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>2.45%</t>
+          <t>2.48%</t>
         </is>
       </c>
     </row>
@@ -924,7 +924,7 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>2.02%</t>
+          <t>1.90%</t>
         </is>
       </c>
     </row>
@@ -953,39 +953,39 @@
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>3189</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>景碩</t>
+          <t>健策</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>3,217,000</t>
+          <t>780,000</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>1.65%</t>
+          <t>1.64%</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>3653</t>
+          <t>3533</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>健策</t>
+          <t>嘉澤</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>780,000</t>
+          <t>1,240,000</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
@@ -997,17 +997,17 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>3533</t>
+          <t>3189</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>嘉澤</t>
+          <t>景碩</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>1,240,000</t>
+          <t>3,217,000</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
@@ -1034,7 +1034,7 @@
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>1.50%</t>
+          <t>1.38%</t>
         </is>
       </c>
     </row>
@@ -1056,7 +1056,7 @@
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>1.48%</t>
+          <t>1.36%</t>
         </is>
       </c>
     </row>
@@ -1078,7 +1078,7 @@
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>1.37%</t>
+          <t>1.35%</t>
         </is>
       </c>
     </row>
@@ -1100,24 +1100,24 @@
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>1.20%</t>
+          <t>1.24%</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>8996</t>
+          <t>7769</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>高力</t>
+          <t>鴻勁</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>1,600,000</t>
+          <t>279,000</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
@@ -1129,149 +1129,149 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>7769</t>
+          <t>8996</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>鴻勁</t>
+          <t>高力</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>279,000</t>
+          <t>1,600,000</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>1.14%</t>
+          <t>1.11%</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>2337</t>
+          <t>2360</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>旺宏</t>
+          <t>致茂</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>10,000,000</t>
+          <t>680,000</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>0.90%</t>
+          <t>0.84%</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>6515</t>
+          <t>2337</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>穎崴</t>
+          <t>旺宏</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>200,000</t>
+          <t>10,000,000</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>0.88%</t>
+          <t>0.84%</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>5274</t>
+          <t>6515</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>信驊</t>
+          <t>穎崴</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>79,500</t>
+          <t>200,000</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>0.67%</t>
+          <t>0.83%</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>2360</t>
+          <t>5274</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>致茂</t>
+          <t>信驊</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>540,000</t>
+          <t>94,500</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>0.63%</t>
+          <t>0.81%</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>8358</t>
+          <t>6805</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>金居</t>
+          <t>富世達</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>1,750,000</t>
+          <t>570,000</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>0.49%</t>
+          <t>0.50%</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>6805</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>富世達</t>
+          <t>鴻海</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>570,000</t>
+          <t>3,200,000</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
@@ -1305,22 +1305,22 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>8358</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>金居</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>3,200,000</t>
+          <t>1,750,000</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>0.46%</t>
+          <t>0.47%</t>
         </is>
       </c>
     </row>
@@ -1349,66 +1349,66 @@
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>1560</t>
+          <t>3665</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>中砂</t>
+          <t>貿聯-KY</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>1,000,000</t>
+          <t>300,000</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>0.45%</t>
+          <t>0.36%</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>4966</t>
+          <t>1560</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>譜瑞-KY</t>
+          <t>中砂</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>800,000</t>
+          <t>750,000</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>0.31%</t>
+          <t>0.34%</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>3665</t>
+          <t>4966</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>貿聯-KY</t>
+          <t>譜瑞-KY</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>250,000</t>
+          <t>800,000</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>0.29%</t>
+          <t>0.31%</t>
         </is>
       </c>
     </row>
@@ -1430,7 +1430,7 @@
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>0.28%</t>
+          <t>0.26%</t>
         </is>
       </c>
     </row>
@@ -1452,7 +1452,7 @@
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>0.26%</t>
+          <t>0.25%</t>
         </is>
       </c>
     </row>
@@ -1474,7 +1474,7 @@
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>0.20%</t>
+          <t>0.21%</t>
         </is>
       </c>
     </row>
@@ -1496,73 +1496,73 @@
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>0.17%</t>
+          <t>0.18%</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>2455</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>450,000</t>
+          <t>60,000</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>0.09%</t>
+          <t>0.16%</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>3264</t>
+          <t>2455</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>欣銓</t>
+          <t>全新</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>600,000</t>
+          <t>450,000</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>0.08%</t>
+          <t>0.09%</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>3264</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>欣銓</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>30,000</t>
+          <t>600,000</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>0.07%</t>
+          <t>0.09%</t>
         </is>
       </c>
     </row>
@@ -1591,12 +1591,12 @@
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>8210</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>世界</t>
+          <t>勤誠</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
@@ -1613,12 +1613,12 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>6147</t>
+          <t>8299</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>頎邦</t>
+          <t>群聯</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
@@ -1635,12 +1635,12 @@
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>6196</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>帆宣</t>
+          <t>世界</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
@@ -1657,12 +1657,12 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>8210</t>
+          <t>6147</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>勤誠</t>
+          <t>頎邦</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
@@ -1679,12 +1679,12 @@
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>8299</t>
+          <t>6196</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>群聯</t>
+          <t>帆宣</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>7,787,449,083</t>
+          <t>7,306,156,280</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr"/>
@@ -1747,7 +1747,7 @@
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>-1,993,602,988</t>
+          <t>-2,114,099,395</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr"/>
